--- a/database/event/6809/event_6809_evp_summary.xlsx
+++ b/database/event/6809/event_6809_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>7.4272</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>4.9597</v>
       </c>
       <c r="D2" t="n">
         <v>2.5791</v>
@@ -545,7 +545,7 @@
         <v>7.1609</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>4.7819</v>
       </c>
       <c r="D3" t="n">
         <v>2.4715</v>
@@ -591,7 +591,7 @@
         <v>7.1013</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>4.7421</v>
       </c>
       <c r="D4" t="n">
         <v>2.4474</v>
@@ -637,7 +637,7 @@
         <v>6.061</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>4.0474</v>
       </c>
       <c r="D5" t="n">
         <v>2.0271</v>
@@ -683,7 +683,7 @@
         <v>6.0298</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>4.0266</v>
       </c>
       <c r="D6" t="n">
         <v>2.0145</v>
@@ -729,7 +729,7 @@
         <v>5.7349</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>3.8296</v>
       </c>
       <c r="D7" t="n">
         <v>1.8954</v>
@@ -775,7 +775,7 @@
         <v>5.1414</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>3.4333</v>
       </c>
       <c r="D8" t="n">
         <v>1.6556</v>
@@ -821,7 +821,7 @@
         <v>4.3446</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>2.9012</v>
       </c>
       <c r="D9" t="n">
         <v>1.3338</v>
@@ -867,7 +867,7 @@
         <v>4.0303</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>2.6913</v>
       </c>
       <c r="D10" t="n">
         <v>1.2068</v>
@@ -913,7 +913,7 @@
         <v>4.028</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>2.6898</v>
       </c>
       <c r="D11" t="n">
         <v>1.2059</v>
@@ -959,7 +959,7 @@
         <v>3.8503</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>2.5711</v>
       </c>
       <c r="D12" t="n">
         <v>1.1341</v>
@@ -1005,7 +1005,7 @@
         <v>3.6987</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>2.4699</v>
       </c>
       <c r="D13" t="n">
         <v>1.0728</v>
@@ -1051,7 +1051,7 @@
         <v>3.542</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>2.3653</v>
       </c>
       <c r="D14" t="n">
         <v>1.0095</v>
@@ -1097,7 +1097,7 @@
         <v>3.1323</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>2.0917</v>
       </c>
       <c r="D15" t="n">
         <v>0.844</v>
@@ -1143,7 +1143,7 @@
         <v>2.9555</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1.9736</v>
       </c>
       <c r="D16" t="n">
         <v>0.7726</v>
@@ -1189,7 +1189,7 @@
         <v>2.9143</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1.9461</v>
       </c>
       <c r="D17" t="n">
         <v>0.756</v>
@@ -1235,7 +1235,7 @@
         <v>2.7064</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1.8073</v>
       </c>
       <c r="D18" t="n">
         <v>0.672</v>
@@ -1281,7 +1281,7 @@
         <v>2.6599</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1.7762</v>
       </c>
       <c r="D19" t="n">
         <v>0.6532</v>
@@ -1327,7 +1327,7 @@
         <v>2.5883</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1.7284</v>
       </c>
       <c r="D20" t="n">
         <v>0.6243</v>
@@ -1373,7 +1373,7 @@
         <v>2.566</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1.7135</v>
       </c>
       <c r="D21" t="n">
         <v>0.6152</v>
@@ -1419,7 +1419,7 @@
         <v>2.5466</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1.7006</v>
       </c>
       <c r="D22" t="n">
         <v>0.6074000000000001</v>
@@ -1465,7 +1465,7 @@
         <v>2.2239</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1.4851</v>
       </c>
       <c r="D23" t="n">
         <v>0.477</v>
@@ -1511,7 +1511,7 @@
         <v>2.1055</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1.406</v>
       </c>
       <c r="D24" t="n">
         <v>0.4292</v>
@@ -1557,7 +1557,7 @@
         <v>2.0826</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1.3907</v>
       </c>
       <c r="D25" t="n">
         <v>0.42</v>
@@ -1603,7 +1603,7 @@
         <v>1.9239</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1.2847</v>
       </c>
       <c r="D26" t="n">
         <v>0.3559</v>
@@ -1649,7 +1649,7 @@
         <v>1.9005</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>1.2691</v>
       </c>
       <c r="D27" t="n">
         <v>0.3464</v>
@@ -1695,7 +1695,7 @@
         <v>1.8195</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>1.215</v>
       </c>
       <c r="D28" t="n">
         <v>0.3137</v>
@@ -1741,7 +1741,7 @@
         <v>1.7775</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>1.187</v>
       </c>
       <c r="D29" t="n">
         <v>0.2967</v>
@@ -1787,7 +1787,7 @@
         <v>1.7172</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>1.1467</v>
       </c>
       <c r="D30" t="n">
         <v>0.2723</v>
@@ -1833,7 +1833,7 @@
         <v>1.7096</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>1.1416</v>
       </c>
       <c r="D31" t="n">
         <v>0.2693</v>
@@ -1879,7 +1879,7 @@
         <v>1.6235</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>1.0841</v>
       </c>
       <c r="D32" t="n">
         <v>0.2345</v>
@@ -1925,7 +1925,7 @@
         <v>1.5552</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>1.0385</v>
       </c>
       <c r="D33" t="n">
         <v>0.2069</v>
@@ -1971,7 +1971,7 @@
         <v>1.5107</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>1.0088</v>
       </c>
       <c r="D34" t="n">
         <v>0.1889</v>
@@ -2017,7 +2017,7 @@
         <v>1.4844</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>0.9912</v>
       </c>
       <c r="D35" t="n">
         <v>0.1783</v>
@@ -2063,7 +2063,7 @@
         <v>1.4312</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>0.9557</v>
       </c>
       <c r="D36" t="n">
         <v>0.1568</v>
@@ -2109,7 +2109,7 @@
         <v>1.3676</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>0.9133</v>
       </c>
       <c r="D37" t="n">
         <v>0.1311</v>
@@ -2155,7 +2155,7 @@
         <v>1.2335</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.8237</v>
       </c>
       <c r="D38" t="n">
         <v>0.0769</v>
@@ -2201,7 +2201,7 @@
         <v>1.2183</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>0.8136</v>
       </c>
       <c r="D39" t="n">
         <v>0.0708</v>
@@ -2247,7 +2247,7 @@
         <v>1.1536</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>0.7703</v>
       </c>
       <c r="D40" t="n">
         <v>0.0447</v>
@@ -2293,7 +2293,7 @@
         <v>1.0099</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>0.6744</v>
       </c>
       <c r="D41" t="n">
         <v>-0.0134</v>
@@ -2339,7 +2339,7 @@
         <v>0.928</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>0.6197</v>
       </c>
       <c r="D42" t="n">
         <v>-0.0465</v>
@@ -2385,7 +2385,7 @@
         <v>0.7523</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>0.5024</v>
       </c>
       <c r="D43" t="n">
         <v>-0.1174</v>
@@ -2431,7 +2431,7 @@
         <v>0.6999</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>0.4674</v>
       </c>
       <c r="D44" t="n">
         <v>-0.1386</v>
@@ -2477,7 +2477,7 @@
         <v>0.6957</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>0.4646</v>
       </c>
       <c r="D45" t="n">
         <v>-0.1403</v>
@@ -2523,7 +2523,7 @@
         <v>0.6335</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>0.423</v>
       </c>
       <c r="D46" t="n">
         <v>-0.1654</v>
@@ -2569,7 +2569,7 @@
         <v>0.4631</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>0.3092</v>
       </c>
       <c r="D47" t="n">
         <v>-0.2343</v>
@@ -2615,7 +2615,7 @@
         <v>0.3963</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>0.2646</v>
       </c>
       <c r="D48" t="n">
         <v>-0.2613</v>
@@ -2661,7 +2661,7 @@
         <v>0.2367</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>0.1581</v>
       </c>
       <c r="D49" t="n">
         <v>-0.3257</v>
@@ -2707,7 +2707,7 @@
         <v>0.213</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>0.1422</v>
       </c>
       <c r="D50" t="n">
         <v>-0.3353</v>
@@ -2753,7 +2753,7 @@
         <v>-0.009299999999999999</v>
       </c>
       <c r="C51" t="n">
-        <v>-0</v>
+        <v>-0.0062</v>
       </c>
       <c r="D51" t="n">
         <v>-0.4251</v>
@@ -2799,7 +2799,7 @@
         <v>-0.1164</v>
       </c>
       <c r="C52" t="n">
-        <v>-0</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="D52" t="n">
         <v>-0.4684</v>
@@ -2845,7 +2845,7 @@
         <v>-0.1306</v>
       </c>
       <c r="C53" t="n">
-        <v>-0</v>
+        <v>-0.0872</v>
       </c>
       <c r="D53" t="n">
         <v>-0.4741</v>
@@ -2891,7 +2891,7 @@
         <v>-0.203</v>
       </c>
       <c r="C54" t="n">
-        <v>-0</v>
+        <v>-0.1356</v>
       </c>
       <c r="D54" t="n">
         <v>-0.5034</v>
@@ -2937,7 +2937,7 @@
         <v>-0.4157</v>
       </c>
       <c r="C55" t="n">
-        <v>-0</v>
+        <v>-0.2776</v>
       </c>
       <c r="D55" t="n">
         <v>-0.5893</v>
@@ -2983,7 +2983,7 @@
         <v>-0.4393</v>
       </c>
       <c r="C56" t="n">
-        <v>-0</v>
+        <v>-0.2934</v>
       </c>
       <c r="D56" t="n">
         <v>-0.5988</v>
@@ -3029,7 +3029,7 @@
         <v>-0.4733</v>
       </c>
       <c r="C57" t="n">
-        <v>-0</v>
+        <v>-0.3161</v>
       </c>
       <c r="D57" t="n">
         <v>-0.6126</v>
@@ -3075,7 +3075,7 @@
         <v>-0.4798</v>
       </c>
       <c r="C58" t="n">
-        <v>-0</v>
+        <v>-0.3204</v>
       </c>
       <c r="D58" t="n">
         <v>-0.6152</v>
@@ -3121,7 +3121,7 @@
         <v>-0.5017</v>
       </c>
       <c r="C59" t="n">
-        <v>-0</v>
+        <v>-0.335</v>
       </c>
       <c r="D59" t="n">
         <v>-0.624</v>
@@ -3167,7 +3167,7 @@
         <v>-0.5024</v>
       </c>
       <c r="C60" t="n">
-        <v>-0</v>
+        <v>-0.3355</v>
       </c>
       <c r="D60" t="n">
         <v>-0.6243</v>
@@ -3213,7 +3213,7 @@
         <v>-0.5101</v>
       </c>
       <c r="C61" t="n">
-        <v>-0</v>
+        <v>-0.3406</v>
       </c>
       <c r="D61" t="n">
         <v>-0.6274</v>
@@ -3259,7 +3259,7 @@
         <v>-0.6709000000000001</v>
       </c>
       <c r="C62" t="n">
-        <v>-0</v>
+        <v>-0.448</v>
       </c>
       <c r="D62" t="n">
         <v>-0.6924</v>
@@ -3305,7 +3305,7 @@
         <v>-0.9785</v>
       </c>
       <c r="C63" t="n">
-        <v>-0</v>
+        <v>-0.6534</v>
       </c>
       <c r="D63" t="n">
         <v>-0.8167</v>
@@ -3351,7 +3351,7 @@
         <v>-1</v>
       </c>
       <c r="C64" t="n">
-        <v>-0</v>
+        <v>-0.6677999999999999</v>
       </c>
       <c r="D64" t="n">
         <v>-0.8253</v>
@@ -3397,7 +3397,7 @@
         <v>-1.0671</v>
       </c>
       <c r="C65" t="n">
-        <v>-0</v>
+        <v>-0.7126</v>
       </c>
       <c r="D65" t="n">
         <v>-0.8524</v>
@@ -3443,7 +3443,7 @@
         <v>-1.0879</v>
       </c>
       <c r="C66" t="n">
-        <v>-0</v>
+        <v>-0.7265</v>
       </c>
       <c r="D66" t="n">
         <v>-0.8608</v>
@@ -3489,7 +3489,7 @@
         <v>-1.0917</v>
       </c>
       <c r="C67" t="n">
-        <v>-0</v>
+        <v>-0.729</v>
       </c>
       <c r="D67" t="n">
         <v>-0.8624000000000001</v>
@@ -3535,7 +3535,7 @@
         <v>-1.1445</v>
       </c>
       <c r="C68" t="n">
-        <v>-0</v>
+        <v>-0.7643</v>
       </c>
       <c r="D68" t="n">
         <v>-0.8837</v>
@@ -3581,7 +3581,7 @@
         <v>-1.1643</v>
       </c>
       <c r="C69" t="n">
-        <v>-0</v>
+        <v>-0.7775</v>
       </c>
       <c r="D69" t="n">
         <v>-0.8917</v>
@@ -3627,7 +3627,7 @@
         <v>-1.2434</v>
       </c>
       <c r="C70" t="n">
-        <v>-0</v>
+        <v>-0.8303</v>
       </c>
       <c r="D70" t="n">
         <v>-0.9237</v>
@@ -3673,7 +3673,7 @@
         <v>-1.2784</v>
       </c>
       <c r="C71" t="n">
-        <v>-0</v>
+        <v>-0.8537</v>
       </c>
       <c r="D71" t="n">
         <v>-0.9378</v>
@@ -3719,7 +3719,7 @@
         <v>-1.503</v>
       </c>
       <c r="C72" t="n">
-        <v>-0</v>
+        <v>-1.0037</v>
       </c>
       <c r="D72" t="n">
         <v>-1.0285</v>
@@ -3765,7 +3765,7 @@
         <v>-1.582</v>
       </c>
       <c r="C73" t="n">
-        <v>-0</v>
+        <v>-1.0564</v>
       </c>
       <c r="D73" t="n">
         <v>-1.0605</v>
@@ -3811,7 +3811,7 @@
         <v>-1.7245</v>
       </c>
       <c r="C74" t="n">
-        <v>-0</v>
+        <v>-1.1516</v>
       </c>
       <c r="D74" t="n">
         <v>-1.118</v>
@@ -3857,7 +3857,7 @@
         <v>-1.8052</v>
       </c>
       <c r="C75" t="n">
-        <v>-0</v>
+        <v>-1.2055</v>
       </c>
       <c r="D75" t="n">
         <v>-1.1506</v>
@@ -3903,7 +3903,7 @@
         <v>-2.3096</v>
       </c>
       <c r="C76" t="n">
-        <v>-0</v>
+        <v>-1.5423</v>
       </c>
       <c r="D76" t="n">
         <v>-1.3544</v>
@@ -3949,7 +3949,7 @@
         <v>-2.3096</v>
       </c>
       <c r="C77" t="n">
-        <v>-0</v>
+        <v>-1.5423</v>
       </c>
       <c r="D77" t="n">
         <v>-1.3544</v>
@@ -3995,7 +3995,7 @@
         <v>-2.4725</v>
       </c>
       <c r="C78" t="n">
-        <v>-0</v>
+        <v>-1.6511</v>
       </c>
       <c r="D78" t="n">
         <v>-1.4202</v>
@@ -4041,7 +4041,7 @@
         <v>-2.6436</v>
       </c>
       <c r="C79" t="n">
-        <v>-0</v>
+        <v>-1.7653</v>
       </c>
       <c r="D79" t="n">
         <v>-1.4893</v>
@@ -4087,7 +4087,7 @@
         <v>-3.2676</v>
       </c>
       <c r="C80" t="n">
-        <v>-0</v>
+        <v>-2.182</v>
       </c>
       <c r="D80" t="n">
         <v>-1.7414</v>
@@ -4133,7 +4133,7 @@
         <v>-3.7003</v>
       </c>
       <c r="C81" t="n">
-        <v>-0</v>
+        <v>-2.471</v>
       </c>
       <c r="D81" t="n">
         <v>-1.9162</v>
@@ -4179,7 +4179,7 @@
         <v>-5.1209</v>
       </c>
       <c r="C82" t="n">
-        <v>-0</v>
+        <v>-3.4196</v>
       </c>
       <c r="D82" t="n">
         <v>-2.4901</v>

--- a/database/event/6809/event_6809_evp_summary.xlsx
+++ b/database/event/6809/event_6809_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>4.9597</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5791</v>
+        <v>2.5151</v>
       </c>
       <c r="E2" t="n">
         <v>7.4272</v>
@@ -548,7 +548,7 @@
         <v>4.7819</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4715</v>
+        <v>2.409</v>
       </c>
       <c r="E3" t="n">
         <v>7.1609</v>
@@ -594,7 +594,7 @@
         <v>4.7421</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4474</v>
+        <v>2.3852</v>
       </c>
       <c r="E4" t="n">
         <v>7.1013</v>
@@ -640,7 +640,7 @@
         <v>4.0474</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0271</v>
+        <v>1.9708</v>
       </c>
       <c r="E5" t="n">
         <v>6.061</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.0298</v>
+        <v>5.9904</v>
       </c>
       <c r="C6" t="n">
-        <v>4.0266</v>
+        <v>4.0003</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0145</v>
+        <v>1.9427</v>
       </c>
       <c r="E6" t="n">
-        <v>6.0298</v>
+        <v>5.9904</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0004</v>
+        <v>4.961</v>
       </c>
       <c r="G6" t="n">
         <v>1.0294</v>
       </c>
       <c r="H6" t="n">
-        <v>5.5376</v>
+        <v>5.4758</v>
       </c>
       <c r="I6" t="n">
         <v>5.6152</v>
@@ -732,7 +732,7 @@
         <v>3.8296</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8954</v>
+        <v>1.8409</v>
       </c>
       <c r="E7" t="n">
         <v>5.7349</v>
@@ -778,7 +778,7 @@
         <v>3.4333</v>
       </c>
       <c r="D8" t="n">
-        <v>1.6556</v>
+        <v>1.6044</v>
       </c>
       <c r="E8" t="n">
         <v>5.1414</v>
@@ -824,7 +824,7 @@
         <v>2.9012</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3338</v>
+        <v>1.287</v>
       </c>
       <c r="E9" t="n">
         <v>4.3446</v>
@@ -860,93 +860,93 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.0303</v>
+        <v>4.0013</v>
       </c>
       <c r="C10" t="n">
-        <v>2.6913</v>
+        <v>2.672</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2068</v>
+        <v>1.1502</v>
       </c>
       <c r="E10" t="n">
-        <v>4.0303</v>
+        <v>4.0013</v>
       </c>
       <c r="F10" t="n">
-        <v>3.9413</v>
+        <v>3.5639</v>
       </c>
       <c r="G10" t="n">
-        <v>0.089</v>
+        <v>0.4374</v>
       </c>
       <c r="H10" t="n">
-        <v>3.9413</v>
+        <v>3.5639</v>
       </c>
       <c r="I10" t="n">
-        <v>3.9966</v>
+        <v>3.6241</v>
       </c>
       <c r="J10" t="n">
-        <v>0.089</v>
+        <v>0.4374</v>
       </c>
       <c r="K10" t="n">
-        <v>304</v>
+        <v>278</v>
       </c>
       <c r="L10" t="n">
-        <v>57</v>
+        <v>140</v>
       </c>
       <c r="M10" t="n">
-        <v>4.0856</v>
+        <v>4.0615</v>
       </c>
       <c r="N10" t="n">
-        <v>361</v>
+        <v>418</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.028</v>
+        <v>3.9863</v>
       </c>
       <c r="C11" t="n">
-        <v>2.6898</v>
+        <v>2.662</v>
       </c>
       <c r="D11" t="n">
-        <v>1.2059</v>
+        <v>1.1442</v>
       </c>
       <c r="E11" t="n">
-        <v>4.028</v>
+        <v>3.9863</v>
       </c>
       <c r="F11" t="n">
-        <v>3.5906</v>
+        <v>3.8973</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4374</v>
+        <v>0.089</v>
       </c>
       <c r="H11" t="n">
-        <v>3.5906</v>
+        <v>3.8973</v>
       </c>
       <c r="I11" t="n">
-        <v>3.6241</v>
+        <v>3.9966</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4374</v>
+        <v>0.089</v>
       </c>
       <c r="K11" t="n">
-        <v>278</v>
+        <v>304</v>
       </c>
       <c r="L11" t="n">
-        <v>140</v>
+        <v>57</v>
       </c>
       <c r="M11" t="n">
-        <v>4.0615</v>
+        <v>4.0856</v>
       </c>
       <c r="N11" t="n">
-        <v>418</v>
+        <v>361</v>
       </c>
     </row>
     <row r="12">
@@ -962,7 +962,7 @@
         <v>2.5711</v>
       </c>
       <c r="D12" t="n">
-        <v>1.1341</v>
+        <v>1.09</v>
       </c>
       <c r="E12" t="n">
         <v>3.8503</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.6987</v>
+        <v>3.6711</v>
       </c>
       <c r="C13" t="n">
-        <v>2.4699</v>
+        <v>2.4515</v>
       </c>
       <c r="D13" t="n">
-        <v>1.0728</v>
+        <v>1.0187</v>
       </c>
       <c r="E13" t="n">
-        <v>3.6987</v>
+        <v>3.6711</v>
       </c>
       <c r="F13" t="n">
-        <v>3.6987</v>
+        <v>3.6711</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>3.6987</v>
+        <v>3.6711</v>
       </c>
       <c r="I13" t="n">
         <v>3.7332</v>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.542</v>
+        <v>3.499</v>
       </c>
       <c r="C14" t="n">
-        <v>2.3653</v>
+        <v>2.3366</v>
       </c>
       <c r="D14" t="n">
-        <v>1.0095</v>
+        <v>0.9500999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>3.542</v>
+        <v>3.499</v>
       </c>
       <c r="F14" t="n">
-        <v>3.8605</v>
+        <v>3.8175</v>
       </c>
       <c r="G14" t="n">
         <v>-0.3185</v>
       </c>
       <c r="H14" t="n">
-        <v>3.8605</v>
+        <v>3.8175</v>
       </c>
       <c r="I14" t="n">
         <v>3.9147</v>
@@ -1100,7 +1100,7 @@
         <v>2.0917</v>
       </c>
       <c r="D15" t="n">
-        <v>0.844</v>
+        <v>0.804</v>
       </c>
       <c r="E15" t="n">
         <v>3.1323</v>
@@ -1146,7 +1146,7 @@
         <v>1.9736</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7726</v>
+        <v>0.7336</v>
       </c>
       <c r="E16" t="n">
         <v>2.9555</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.9143</v>
+        <v>2.9034</v>
       </c>
       <c r="C17" t="n">
-        <v>1.9461</v>
+        <v>1.9388</v>
       </c>
       <c r="D17" t="n">
-        <v>0.756</v>
+        <v>0.7128</v>
       </c>
       <c r="E17" t="n">
-        <v>2.9143</v>
+        <v>2.9034</v>
       </c>
       <c r="F17" t="n">
-        <v>2.9143</v>
+        <v>2.9034</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.9143</v>
+        <v>2.9034</v>
       </c>
       <c r="I17" t="n">
         <v>2.9278</v>
@@ -1232,25 +1232,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.7064</v>
+        <v>2.68</v>
       </c>
       <c r="C18" t="n">
-        <v>1.8073</v>
+        <v>1.7896</v>
       </c>
       <c r="D18" t="n">
-        <v>0.672</v>
+        <v>0.6238</v>
       </c>
       <c r="E18" t="n">
-        <v>2.7064</v>
+        <v>2.68</v>
       </c>
       <c r="F18" t="n">
-        <v>3.5417</v>
+        <v>3.5153</v>
       </c>
       <c r="G18" t="n">
         <v>-0.8353</v>
       </c>
       <c r="H18" t="n">
-        <v>3.5417</v>
+        <v>3.5153</v>
       </c>
       <c r="I18" t="n">
         <v>3.5747</v>
@@ -1284,7 +1284,7 @@
         <v>1.7762</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6532</v>
+        <v>0.6158</v>
       </c>
       <c r="E19" t="n">
         <v>2.6599</v>
@@ -1330,7 +1330,7 @@
         <v>1.7284</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6243</v>
+        <v>0.5873</v>
       </c>
       <c r="E20" t="n">
         <v>2.5883</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.566</v>
+        <v>2.5564</v>
       </c>
       <c r="C21" t="n">
-        <v>1.7135</v>
+        <v>1.7071</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6152</v>
+        <v>0.5746</v>
       </c>
       <c r="E21" t="n">
-        <v>2.566</v>
+        <v>2.5564</v>
       </c>
       <c r="F21" t="n">
-        <v>2.566</v>
+        <v>2.5564</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2.566</v>
+        <v>2.5564</v>
       </c>
       <c r="I21" t="n">
         <v>2.5779</v>
@@ -1416,25 +1416,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.5466</v>
+        <v>2.5277</v>
       </c>
       <c r="C22" t="n">
-        <v>1.7006</v>
+        <v>1.6879</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6074000000000001</v>
+        <v>0.5631</v>
       </c>
       <c r="E22" t="n">
-        <v>2.5466</v>
+        <v>2.5277</v>
       </c>
       <c r="F22" t="n">
-        <v>2.5466</v>
+        <v>2.5277</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2.5466</v>
+        <v>2.5277</v>
       </c>
       <c r="I22" t="n">
         <v>2.5704</v>
@@ -1468,7 +1468,7 @@
         <v>1.4851</v>
       </c>
       <c r="D23" t="n">
-        <v>0.477</v>
+        <v>0.4421</v>
       </c>
       <c r="E23" t="n">
         <v>2.2239</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.1055</v>
+        <v>2.0912</v>
       </c>
       <c r="C24" t="n">
-        <v>1.406</v>
+        <v>1.3965</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4292</v>
+        <v>0.3892</v>
       </c>
       <c r="E24" t="n">
-        <v>2.1055</v>
+        <v>2.0912</v>
       </c>
       <c r="F24" t="n">
-        <v>1.9294</v>
+        <v>1.9151</v>
       </c>
       <c r="G24" t="n">
         <v>0.1761</v>
       </c>
       <c r="H24" t="n">
-        <v>1.9294</v>
+        <v>1.9151</v>
       </c>
       <c r="I24" t="n">
         <v>1.9474</v>
@@ -1554,25 +1554,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.0826</v>
+        <v>2.0671</v>
       </c>
       <c r="C25" t="n">
-        <v>1.3907</v>
+        <v>1.3804</v>
       </c>
       <c r="D25" t="n">
-        <v>0.42</v>
+        <v>0.3796</v>
       </c>
       <c r="E25" t="n">
-        <v>2.0826</v>
+        <v>2.0671</v>
       </c>
       <c r="F25" t="n">
-        <v>2.0826</v>
+        <v>2.0671</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>2.0826</v>
+        <v>2.0671</v>
       </c>
       <c r="I25" t="n">
         <v>2.102</v>
@@ -1606,7 +1606,7 @@
         <v>1.2847</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3559</v>
+        <v>0.3226</v>
       </c>
       <c r="E26" t="n">
         <v>1.9239</v>
@@ -1652,7 +1652,7 @@
         <v>1.2691</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3464</v>
+        <v>0.3132</v>
       </c>
       <c r="E27" t="n">
         <v>1.9005</v>
@@ -1698,7 +1698,7 @@
         <v>1.215</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3137</v>
+        <v>0.281</v>
       </c>
       <c r="E28" t="n">
         <v>1.8195</v>
@@ -1738,25 +1738,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.7775</v>
+        <v>1.7657</v>
       </c>
       <c r="C29" t="n">
-        <v>1.187</v>
+        <v>1.1791</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2967</v>
+        <v>0.2595</v>
       </c>
       <c r="E29" t="n">
-        <v>1.7775</v>
+        <v>1.7657</v>
       </c>
       <c r="F29" t="n">
-        <v>1.59</v>
+        <v>1.5782</v>
       </c>
       <c r="G29" t="n">
         <v>0.1875</v>
       </c>
       <c r="H29" t="n">
-        <v>1.59</v>
+        <v>1.5782</v>
       </c>
       <c r="I29" t="n">
         <v>1.6048</v>
@@ -1790,7 +1790,7 @@
         <v>1.1467</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2723</v>
+        <v>0.2402</v>
       </c>
       <c r="E30" t="n">
         <v>1.7172</v>
@@ -1830,25 +1830,25 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.7096</v>
+        <v>1.7033</v>
       </c>
       <c r="C31" t="n">
-        <v>1.1416</v>
+        <v>1.1374</v>
       </c>
       <c r="D31" t="n">
-        <v>0.2693</v>
+        <v>0.2347</v>
       </c>
       <c r="E31" t="n">
-        <v>1.7096</v>
+        <v>1.7033</v>
       </c>
       <c r="F31" t="n">
-        <v>1.7096</v>
+        <v>1.7033</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.7096</v>
+        <v>1.7033</v>
       </c>
       <c r="I31" t="n">
         <v>1.7176</v>
@@ -1882,7 +1882,7 @@
         <v>1.0841</v>
       </c>
       <c r="D32" t="n">
-        <v>0.2345</v>
+        <v>0.2029</v>
       </c>
       <c r="E32" t="n">
         <v>1.6235</v>
@@ -1928,7 +1928,7 @@
         <v>1.0385</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2069</v>
+        <v>0.1757</v>
       </c>
       <c r="E33" t="n">
         <v>1.5552</v>
@@ -1974,7 +1974,7 @@
         <v>1.0088</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1889</v>
+        <v>0.158</v>
       </c>
       <c r="E34" t="n">
         <v>1.5107</v>
@@ -2014,25 +2014,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.4844</v>
+        <v>1.4789</v>
       </c>
       <c r="C35" t="n">
-        <v>0.9912</v>
+        <v>0.9876</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1783</v>
+        <v>0.1453</v>
       </c>
       <c r="E35" t="n">
-        <v>1.4844</v>
+        <v>1.4789</v>
       </c>
       <c r="F35" t="n">
-        <v>1.4844</v>
+        <v>1.4789</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.4844</v>
+        <v>1.4789</v>
       </c>
       <c r="I35" t="n">
         <v>1.4914</v>
@@ -2066,7 +2066,7 @@
         <v>0.9557</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1568</v>
+        <v>0.1263</v>
       </c>
       <c r="E36" t="n">
         <v>1.4312</v>
@@ -2112,7 +2112,7 @@
         <v>0.9133</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1311</v>
+        <v>0.1009</v>
       </c>
       <c r="E37" t="n">
         <v>1.3676</v>
@@ -2152,25 +2152,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.2335</v>
+        <v>1.2162</v>
       </c>
       <c r="C38" t="n">
-        <v>0.8237</v>
+        <v>0.8122</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0769</v>
+        <v>0.0406</v>
       </c>
       <c r="E38" t="n">
-        <v>1.2335</v>
+        <v>1.2162</v>
       </c>
       <c r="F38" t="n">
-        <v>1.5584</v>
+        <v>1.5411</v>
       </c>
       <c r="G38" t="n">
         <v>-0.3249</v>
       </c>
       <c r="H38" t="n">
-        <v>1.5584</v>
+        <v>1.5411</v>
       </c>
       <c r="I38" t="n">
         <v>1.5803</v>
@@ -2198,25 +2198,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.2183</v>
+        <v>1.2138</v>
       </c>
       <c r="C39" t="n">
-        <v>0.8136</v>
+        <v>0.8105</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0708</v>
+        <v>0.0397</v>
       </c>
       <c r="E39" t="n">
-        <v>1.2183</v>
+        <v>1.2138</v>
       </c>
       <c r="F39" t="n">
-        <v>1.2183</v>
+        <v>1.2138</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1.2183</v>
+        <v>1.2138</v>
       </c>
       <c r="I39" t="n">
         <v>1.224</v>
@@ -2250,7 +2250,7 @@
         <v>0.7703</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0447</v>
+        <v>0.0157</v>
       </c>
       <c r="E40" t="n">
         <v>1.1536</v>
@@ -2296,7 +2296,7 @@
         <v>0.6744</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.0134</v>
+        <v>-0.0416</v>
       </c>
       <c r="E41" t="n">
         <v>1.0099</v>
@@ -2342,7 +2342,7 @@
         <v>0.6197</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.0465</v>
+        <v>-0.0742</v>
       </c>
       <c r="E42" t="n">
         <v>0.928</v>
@@ -2388,7 +2388,7 @@
         <v>0.5024</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.1174</v>
+        <v>-0.1442</v>
       </c>
       <c r="E43" t="n">
         <v>0.7523</v>
@@ -2434,7 +2434,7 @@
         <v>0.4674</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.1386</v>
+        <v>-0.1651</v>
       </c>
       <c r="E44" t="n">
         <v>0.6999</v>
@@ -2480,7 +2480,7 @@
         <v>0.4646</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.1403</v>
+        <v>-0.1667</v>
       </c>
       <c r="E45" t="n">
         <v>0.6957</v>
@@ -2526,7 +2526,7 @@
         <v>0.423</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.1654</v>
+        <v>-0.1915</v>
       </c>
       <c r="E46" t="n">
         <v>0.6335</v>
@@ -2572,7 +2572,7 @@
         <v>0.3092</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.2343</v>
+        <v>-0.2594</v>
       </c>
       <c r="E47" t="n">
         <v>0.4631</v>
@@ -2618,7 +2618,7 @@
         <v>0.2646</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.2613</v>
+        <v>-0.286</v>
       </c>
       <c r="E48" t="n">
         <v>0.3963</v>
@@ -2664,7 +2664,7 @@
         <v>0.1581</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3257</v>
+        <v>-0.3496</v>
       </c>
       <c r="E49" t="n">
         <v>0.2367</v>
@@ -2704,25 +2704,25 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.213</v>
+        <v>0.2114</v>
       </c>
       <c r="C50" t="n">
-        <v>0.1422</v>
+        <v>0.1412</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.3353</v>
+        <v>-0.3597</v>
       </c>
       <c r="E50" t="n">
-        <v>0.213</v>
+        <v>0.2114</v>
       </c>
       <c r="F50" t="n">
-        <v>0.213</v>
+        <v>0.2114</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.213</v>
+        <v>0.2114</v>
       </c>
       <c r="I50" t="n">
         <v>0.215</v>
@@ -2756,7 +2756,7 @@
         <v>-0.0062</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4251</v>
+        <v>-0.4476</v>
       </c>
       <c r="E51" t="n">
         <v>-0.009299999999999999</v>
@@ -2802,7 +2802,7 @@
         <v>-0.07770000000000001</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4684</v>
+        <v>-0.4903</v>
       </c>
       <c r="E52" t="n">
         <v>-0.1164</v>
@@ -2848,7 +2848,7 @@
         <v>-0.0872</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4741</v>
+        <v>-0.4959</v>
       </c>
       <c r="E53" t="n">
         <v>-0.1306</v>
@@ -2894,7 +2894,7 @@
         <v>-0.1356</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5034</v>
+        <v>-0.5248</v>
       </c>
       <c r="E54" t="n">
         <v>-0.203</v>
@@ -2940,7 +2940,7 @@
         <v>-0.2776</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5893</v>
+        <v>-0.6095</v>
       </c>
       <c r="E55" t="n">
         <v>-0.4157</v>
@@ -2986,7 +2986,7 @@
         <v>-0.2934</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5988</v>
+        <v>-0.6189</v>
       </c>
       <c r="E56" t="n">
         <v>-0.4393</v>
@@ -3032,7 +3032,7 @@
         <v>-0.3161</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.6126</v>
+        <v>-0.6325</v>
       </c>
       <c r="E57" t="n">
         <v>-0.4733</v>
@@ -3078,7 +3078,7 @@
         <v>-0.3204</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6152</v>
+        <v>-0.6351</v>
       </c>
       <c r="E58" t="n">
         <v>-0.4798</v>
@@ -3124,7 +3124,7 @@
         <v>-0.335</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.624</v>
+        <v>-0.6438</v>
       </c>
       <c r="E59" t="n">
         <v>-0.5017</v>
@@ -3170,7 +3170,7 @@
         <v>-0.3355</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6243</v>
+        <v>-0.6441</v>
       </c>
       <c r="E60" t="n">
         <v>-0.5024</v>
@@ -3210,25 +3210,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.5101</v>
+        <v>-0.5092</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.3406</v>
+        <v>-0.34</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6274</v>
+        <v>-0.6468</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.5101</v>
+        <v>-0.5092</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.0847</v>
+        <v>-0.0838</v>
       </c>
       <c r="G61" t="n">
         <v>-0.4254</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.0847</v>
+        <v>-0.0838</v>
       </c>
       <c r="I61" t="n">
         <v>-0.0859</v>
@@ -3262,7 +3262,7 @@
         <v>-0.448</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6924</v>
+        <v>-0.7112000000000001</v>
       </c>
       <c r="E62" t="n">
         <v>-0.6709000000000001</v>
@@ -3308,7 +3308,7 @@
         <v>-0.6534</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.8167</v>
+        <v>-0.8337</v>
       </c>
       <c r="E63" t="n">
         <v>-0.9785</v>
@@ -3354,7 +3354,7 @@
         <v>-0.6677999999999999</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.8253</v>
+        <v>-0.8423</v>
       </c>
       <c r="E64" t="n">
         <v>-1</v>
@@ -3400,7 +3400,7 @@
         <v>-0.7126</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.8524</v>
+        <v>-0.869</v>
       </c>
       <c r="E65" t="n">
         <v>-1.0671</v>
@@ -3446,7 +3446,7 @@
         <v>-0.7265</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8608</v>
+        <v>-0.8773</v>
       </c>
       <c r="E66" t="n">
         <v>-1.0879</v>
@@ -3492,7 +3492,7 @@
         <v>-0.729</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8624000000000001</v>
+        <v>-0.8788</v>
       </c>
       <c r="E67" t="n">
         <v>-1.0917</v>
@@ -3538,7 +3538,7 @@
         <v>-0.7643</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8837</v>
+        <v>-0.8999</v>
       </c>
       <c r="E68" t="n">
         <v>-1.1445</v>
@@ -3584,7 +3584,7 @@
         <v>-0.7775</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8917</v>
+        <v>-0.9078000000000001</v>
       </c>
       <c r="E69" t="n">
         <v>-1.1643</v>
@@ -3630,7 +3630,7 @@
         <v>-0.8303</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9237</v>
+        <v>-0.9393</v>
       </c>
       <c r="E70" t="n">
         <v>-1.2434</v>
@@ -3676,7 +3676,7 @@
         <v>-0.8537</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9378</v>
+        <v>-0.9532</v>
       </c>
       <c r="E71" t="n">
         <v>-1.2784</v>
@@ -3722,7 +3722,7 @@
         <v>-1.0037</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.0285</v>
+        <v>-1.0427</v>
       </c>
       <c r="E72" t="n">
         <v>-1.503</v>
@@ -3768,7 +3768,7 @@
         <v>-1.0564</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0605</v>
+        <v>-1.0742</v>
       </c>
       <c r="E73" t="n">
         <v>-1.582</v>
@@ -3814,7 +3814,7 @@
         <v>-1.1516</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.118</v>
+        <v>-1.131</v>
       </c>
       <c r="E74" t="n">
         <v>-1.7245</v>
@@ -3860,7 +3860,7 @@
         <v>-1.2055</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.1506</v>
+        <v>-1.1631</v>
       </c>
       <c r="E75" t="n">
         <v>-1.8052</v>
@@ -3906,7 +3906,7 @@
         <v>-1.5423</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.3544</v>
+        <v>-1.3641</v>
       </c>
       <c r="E76" t="n">
         <v>-2.3096</v>
@@ -3952,7 +3952,7 @@
         <v>-1.5423</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.3544</v>
+        <v>-1.3641</v>
       </c>
       <c r="E77" t="n">
         <v>-2.3096</v>
@@ -3998,7 +3998,7 @@
         <v>-1.6511</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.4202</v>
+        <v>-1.429</v>
       </c>
       <c r="E78" t="n">
         <v>-2.4725</v>
@@ -4044,7 +4044,7 @@
         <v>-1.7653</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.4893</v>
+        <v>-1.4971</v>
       </c>
       <c r="E79" t="n">
         <v>-2.6436</v>
@@ -4090,7 +4090,7 @@
         <v>-2.182</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.7414</v>
+        <v>-1.7457</v>
       </c>
       <c r="E80" t="n">
         <v>-3.2676</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-3.7003</v>
+        <v>-3.6766</v>
       </c>
       <c r="C81" t="n">
-        <v>-2.471</v>
+        <v>-2.4552</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.9162</v>
+        <v>-1.9087</v>
       </c>
       <c r="E81" t="n">
-        <v>-3.7003</v>
+        <v>-3.6766</v>
       </c>
       <c r="F81" t="n">
-        <v>-3.185</v>
+        <v>-3.1613</v>
       </c>
       <c r="G81" t="n">
         <v>-0.5153</v>
       </c>
       <c r="H81" t="n">
-        <v>-3.185</v>
+        <v>-3.1613</v>
       </c>
       <c r="I81" t="n">
         <v>-3.2147</v>
@@ -4176,25 +4176,25 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-5.1209</v>
+        <v>-5.0828</v>
       </c>
       <c r="C82" t="n">
-        <v>-3.4196</v>
+        <v>-3.3942</v>
       </c>
       <c r="D82" t="n">
-        <v>-2.4901</v>
+        <v>-2.4689</v>
       </c>
       <c r="E82" t="n">
-        <v>-5.1209</v>
+        <v>-5.0828</v>
       </c>
       <c r="F82" t="n">
-        <v>-5.1209</v>
+        <v>-5.0828</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>-5.1209</v>
+        <v>-5.0828</v>
       </c>
       <c r="I82" t="n">
         <v>-5.1687</v>
